--- a/artfynd/A 14565-2026 artfynd.xlsx
+++ b/artfynd/A 14565-2026 artfynd.xlsx
@@ -675,60 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129450309</v>
+        <v>129494018</v>
       </c>
       <c r="B2" t="n">
-        <v>57733</v>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Alstermo, Grönalund, Alstermo, Sm</t>
+          <t>Alstermo, Grönalund, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541238</v>
+        <v>541321</v>
       </c>
       <c r="R2" t="n">
-        <v>6312433</v>
+        <v>6312501</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,19 +755,9 @@
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,18 +766,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Uno Pettersson</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Uno Pettersson, Per Darell</t>
+          <t>Per Darell, Uno Pettersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
